--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,118 @@
           <t>Nordsyd - Naturvärdesinventering åt Svenska kraftnät</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122383068</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57390</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Borgberget, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>595054</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6625343</v>
+      </c>
+      <c r="S4" t="n">
+        <v>200</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västerås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sevalla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>John Wassberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>John Wassberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>122383068</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -927,7 +927,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -938,11 +938,6 @@
       <c r="E4" t="n">
         <v>100049</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Dryocopus martius</t>

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>122383068</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,6 +937,11 @@
       </c>
       <c r="E4" t="n">
         <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>122383068</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 32731-2020 artfynd.xlsx
+++ b/artfynd/A 32731-2020 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>122383068</v>
       </c>
       <c r="B4" t="n">
-        <v>57400</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
